--- a/docs/analytics/2026-08-17-tracking-event-dictionary.xlsx
+++ b/docs/analytics/2026-08-17-tracking-event-dictionary.xlsx
@@ -16,7 +16,7 @@
     <sheet name="风险与待办" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'事件字典'!$A$1:$M$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'事件字典'!$A$1:$M$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -653,7 +653,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>版本 v3.0 ｜ 2026-08-17 ｜ 状态：设计中，待研发评审排期 ｜ v3 变更：新增「余额流水看板(/dashboard)」页面事件、新增「页面事件总览」sheet、修正 4 处重复事件定义</t>
+          <t>版本 v3.1 ｜ 2026-08-17 ｜ 状态：设计中，待研发评审排期 ｜ v3 变更：新增「余额流水看板(/dashboard)」页面事件、新增「页面事件总览」sheet、修正 4 处重复事件定义、新增资金概览卡片点击埋点设计</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10323,17 +10323,17 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>导出与刷新</t>
+          <t>资金概览卡片</t>
         </is>
       </c>
       <c r="C118" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_export_click</t>
+          <t>ledger_dashboard_fund_card_click</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>导出流水点击</t>
+          <t>资金概览卡片点击查看明细</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="F118" s="9" t="inlineStr">
         <is>
-          <t>点击「导出流水」按钮，打开导出范围选择</t>
+          <t>点击「资金概览」区任一张卡片（账户总余额/可用余额/冻结金额/本月充值/本月消耗）</t>
         </is>
       </c>
       <c r="G118" s="9" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="I118" s="23" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>account_id, card_type, card_value</t>
         </is>
       </c>
       <c r="J118" s="9" t="inlineStr">
@@ -10366,13 +10366,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K118" s="9" t="inlineStr"/>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>card_type：total_balance/available_balance/frozen_amount/monthly_recharge/monthly_spend；card_value 为点击时卡片展示的金额原文</t>
+        </is>
+      </c>
       <c r="L118" s="18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M118" s="9" t="inlineStr"/>
+      <c r="M118" s="9" t="inlineStr">
+        <is>
+          <t>当前原型该卡片尚未绑定点击交互与明细视图，此为提前设计的埋点方案，待前端补充「查看明细」功能后再上线</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -10387,12 +10395,12 @@
       </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_export_scope_select</t>
+          <t>ledger_dashboard_export_click</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>导出范围选择</t>
+          <t>导出流水点击</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -10402,7 +10410,7 @@
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>选择「当前筛选结果」或「全部账户本月流水」</t>
+          <t>点击「导出流水」按钮，打开导出范围选择</t>
         </is>
       </c>
       <c r="G119" s="9" t="inlineStr">
@@ -10415,14 +10423,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="19" t="inlineStr">
-        <is>
-          <t>export_scope</t>
+      <c r="I119" s="23" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K119" s="9" t="inlineStr"/>
@@ -10431,11 +10439,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="M119" s="9" t="inlineStr">
-        <is>
-          <t>当前选择后仅关闭弹窗，未接入真实导出下载逻辑</t>
-        </is>
-      </c>
+      <c r="M119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -10450,12 +10454,12 @@
       </c>
       <c r="C120" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_refresh_click</t>
+          <t>ledger_dashboard_export_scope_select</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>刷新数据点击</t>
+          <t>导出范围选择</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -10465,7 +10469,7 @@
       </c>
       <c r="F120" s="9" t="inlineStr">
         <is>
-          <t>点击「刷新数据」按钮</t>
+          <t>选择「当前筛选结果」或「全部账户本月流水」</t>
         </is>
       </c>
       <c r="G120" s="9" t="inlineStr">
@@ -10483,20 +10487,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J120" s="19" t="inlineStr">
+        <is>
+          <t>export_scope</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="L120" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="M120" s="9" t="inlineStr">
         <is>
-          <t>当前 onClick 未绑定，点击无实际刷新效果，暂不建议上线该埋点</t>
+          <t>当前选择后仅关闭弹窗，未接入真实导出下载逻辑</t>
         </is>
       </c>
     </row>
@@ -10508,17 +10512,17 @@
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>流水明细筛选</t>
+          <t>导出与刷新</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_time_range_select</t>
+          <t>ledger_dashboard_refresh_click</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>时间范围筛选</t>
+          <t>刷新数据点击</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
@@ -10528,7 +10532,7 @@
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>流水明细/资金趋势 Tab 内选择时间范围下拉</t>
+          <t>点击「刷新数据」按钮</t>
         </is>
       </c>
       <c r="G121" s="9" t="inlineStr">
@@ -10546,22 +10550,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J121" s="19" t="inlineStr">
-        <is>
-          <t>time_range, tab</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr">
-        <is>
-          <t>近30/60/90日、近半年、近一年等</t>
-        </is>
-      </c>
-      <c r="L121" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M121" s="9" t="inlineStr"/>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr"/>
+      <c r="L121" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>当前 onClick 未绑定，点击无实际刷新效果，暂不建议上线该埋点</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -10576,12 +10580,12 @@
       </c>
       <c r="C122" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_type_select</t>
+          <t>ledger_dashboard_filter_time_range_select</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>流水类型筛选</t>
+          <t>时间范围筛选</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -10591,7 +10595,7 @@
       </c>
       <c r="F122" s="9" t="inlineStr">
         <is>
-          <t>流水明细 Tab 内选择流水类型下拉</t>
+          <t>流水明细/资金趋势 Tab 内选择时间范围下拉</t>
         </is>
       </c>
       <c r="G122" s="9" t="inlineStr">
@@ -10611,12 +10615,12 @@
       </c>
       <c r="J122" s="19" t="inlineStr">
         <is>
-          <t>type_filter</t>
+          <t>time_range, tab</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
         <is>
-          <t>充值入账/广告消耗/冻结/解冻/退款/调整</t>
+          <t>近30/60/90日、近半年、近一年等</t>
         </is>
       </c>
       <c r="L122" s="18" t="inlineStr">
@@ -10639,22 +10643,22 @@
       </c>
       <c r="C123" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_id_input</t>
+          <t>ledger_dashboard_filter_type_select</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>关联单号筛选输入</t>
+          <t>流水类型筛选</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Blur</t>
+          <t>Click</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>流水明细 Tab 内「关联单号」输入框失焦且非空</t>
+          <t>流水明细 Tab 内选择流水类型下拉</t>
         </is>
       </c>
       <c r="G123" s="9" t="inlineStr">
@@ -10662,9 +10666,9 @@
           <t>routes/dashboard.tsx</t>
         </is>
       </c>
-      <c r="H123" s="22" t="inlineStr">
-        <is>
-          <t>recharge_id</t>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="9" t="inlineStr">
@@ -10672,15 +10676,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K123" s="9" t="inlineStr"/>
-      <c r="L123" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="J123" s="19" t="inlineStr">
+        <is>
+          <t>type_filter</t>
+        </is>
+      </c>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>充值入账/广告消耗/冻结/解冻/退款/调整</t>
+        </is>
+      </c>
+      <c r="L123" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="M123" s="9" t="inlineStr"/>
@@ -10698,22 +10706,22 @@
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_search_click</t>
+          <t>ledger_dashboard_filter_id_input</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>查询点击</t>
+          <t>关联单号筛选输入</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>Click</t>
+          <t>Blur</t>
         </is>
       </c>
       <c r="F124" s="9" t="inlineStr">
         <is>
-          <t>流水明细 Tab 内点击「查询」按钮</t>
+          <t>流水明细 Tab 内「关联单号」输入框失焦且非空</t>
         </is>
       </c>
       <c r="G124" s="9" t="inlineStr">
@@ -10721,9 +10729,9 @@
           <t>routes/dashboard.tsx</t>
         </is>
       </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H124" s="22" t="inlineStr">
+        <is>
+          <t>recharge_id</t>
         </is>
       </c>
       <c r="I124" s="9" t="inlineStr">
@@ -10742,11 +10750,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="M124" s="9" t="inlineStr">
-        <is>
-          <t>当前 onClick 未绑定，点击无实际查询效果，暂不建议上线该埋点</t>
-        </is>
-      </c>
+      <c r="M124" s="9" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -10761,12 +10765,12 @@
       </c>
       <c r="C125" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_reset_click</t>
+          <t>ledger_dashboard_search_click</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>重置筛选点击</t>
+          <t>查询点击</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
@@ -10776,7 +10780,7 @@
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>流水明细 Tab 内点击「重置」按钮</t>
+          <t>流水明细 Tab 内点击「查询」按钮</t>
         </is>
       </c>
       <c r="G125" s="9" t="inlineStr">
@@ -10805,7 +10809,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="M125" s="9" t="inlineStr"/>
+      <c r="M125" s="9" t="inlineStr">
+        <is>
+          <t>当前 onClick 未绑定，点击无实际查询效果，暂不建议上线该埋点</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
@@ -10815,17 +10823,17 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>流水详情</t>
+          <t>流水明细筛选</t>
         </is>
       </c>
       <c r="C126" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_row_detail_click</t>
+          <t>ledger_dashboard_reset_click</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>流水行查看详情点击</t>
+          <t>重置筛选点击</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
@@ -10835,7 +10843,7 @@
       </c>
       <c r="F126" s="9" t="inlineStr">
         <is>
-          <t>流水明细表格内点击某行「查看详情」</t>
+          <t>流水明细 Tab 内点击「重置」按钮</t>
         </is>
       </c>
       <c r="G126" s="9" t="inlineStr">
@@ -10843,14 +10851,14 @@
           <t>routes/dashboard.tsx</t>
         </is>
       </c>
-      <c r="H126" s="22" t="inlineStr">
-        <is>
-          <t>recharge_id</t>
-        </is>
-      </c>
-      <c r="I126" s="23" t="inlineStr">
-        <is>
-          <t>account_id</t>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
@@ -10859,16 +10867,12 @@
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr"/>
-      <c r="L126" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M126" s="9" t="inlineStr">
-        <is>
-          <t>打开的是本页内 Sheet 抽屉，非路由跳转</t>
-        </is>
-      </c>
+      <c r="L126" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="M126" s="9" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -10883,22 +10887,22 @@
       </c>
       <c r="C127" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_detail_drawer_view</t>
+          <t>ledger_dashboard_row_detail_click</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>流水详情抽屉曝光</t>
+          <t>流水行查看详情点击</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Expo</t>
+          <t>Click</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>流水详情 Sheet 打开时</t>
+          <t>流水明细表格内点击某行「查看详情」</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
@@ -10922,12 +10926,16 @@
         </is>
       </c>
       <c r="K127" s="9" t="inlineStr"/>
-      <c r="L127" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="M127" s="9" t="inlineStr"/>
+      <c r="L127" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>打开的是本页内 Sheet 抽屉，非路由跳转</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
@@ -10942,22 +10950,22 @@
       </c>
       <c r="C128" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_detail_close_click</t>
+          <t>ledger_dashboard_detail_drawer_view</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>流水详情抽屉关闭点击</t>
+          <t>流水详情抽屉曝光</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Click</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="F128" s="9" t="inlineStr">
         <is>
-          <t>详情抽屉点击「关闭」</t>
+          <t>流水详情 Sheet 打开时</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
@@ -10965,14 +10973,14 @@
           <t>routes/dashboard.tsx</t>
         </is>
       </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H128" s="22" t="inlineStr">
+        <is>
+          <t>recharge_id</t>
+        </is>
+      </c>
+      <c r="I128" s="23" t="inlineStr">
+        <is>
+          <t>account_id</t>
         </is>
       </c>
       <c r="J128" s="9" t="inlineStr">
@@ -10988,8 +10996,67 @@
       </c>
       <c r="M128" s="9" t="inlineStr"/>
     </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>余额流水看板（/dashboard）</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>流水详情</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>ledger_dashboard_detail_close_click</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>流水详情抽屉关闭点击</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>详情抽屉点击「关闭」</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>routes/dashboard.tsx</t>
+        </is>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="9" t="inlineStr"/>
+      <c r="L129" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M128"/>
+  <autoFilter ref="A1:M129"/>
   <mergeCells count="11">
     <mergeCell ref="A46:M46"/>
     <mergeCell ref="A19:M19"/>
@@ -11013,7 +11080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16841,12 +16908,12 @@
       </c>
       <c r="C160" s="9" t="inlineStr">
         <is>
-          <t>导出流水点击</t>
+          <t>资金概览卡片点击查看明细</t>
         </is>
       </c>
       <c r="D160" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_export_click</t>
+          <t>ledger_dashboard_fund_card_click</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
@@ -16878,12 +16945,12 @@
       </c>
       <c r="C161" s="9" t="inlineStr">
         <is>
-          <t>导出范围选择</t>
+          <t>导出流水点击</t>
         </is>
       </c>
       <c r="D161" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_export_scope_select</t>
+          <t>ledger_dashboard_export_click</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
@@ -16915,12 +16982,12 @@
       </c>
       <c r="C162" s="9" t="inlineStr">
         <is>
-          <t>刷新数据点击</t>
+          <t>导出范围选择</t>
         </is>
       </c>
       <c r="D162" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_refresh_click</t>
+          <t>ledger_dashboard_export_scope_select</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
@@ -16928,9 +16995,9 @@
           <t>Click</t>
         </is>
       </c>
-      <c r="F162" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="F162" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G162" s="9" t="inlineStr">
@@ -16952,12 +17019,12 @@
       </c>
       <c r="C163" s="9" t="inlineStr">
         <is>
-          <t>时间范围筛选</t>
+          <t>刷新数据点击</t>
         </is>
       </c>
       <c r="D163" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_time_range_select</t>
+          <t>ledger_dashboard_refresh_click</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
@@ -16965,9 +17032,9 @@
           <t>Click</t>
         </is>
       </c>
-      <c r="F163" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="F163" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="G163" s="9" t="inlineStr">
@@ -16989,12 +17056,12 @@
       </c>
       <c r="C164" s="9" t="inlineStr">
         <is>
-          <t>流水类型筛选</t>
+          <t>时间范围筛选</t>
         </is>
       </c>
       <c r="D164" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_type_select</t>
+          <t>ledger_dashboard_filter_time_range_select</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
@@ -17026,22 +17093,22 @@
       </c>
       <c r="C165" s="9" t="inlineStr">
         <is>
-          <t>关联单号筛选输入</t>
+          <t>流水类型筛选</t>
         </is>
       </c>
       <c r="D165" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_filter_id_input</t>
+          <t>ledger_dashboard_filter_type_select</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>Blur</t>
-        </is>
-      </c>
-      <c r="F165" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F165" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
@@ -17063,17 +17130,17 @@
       </c>
       <c r="C166" s="9" t="inlineStr">
         <is>
-          <t>查询点击</t>
+          <t>关联单号筛选输入</t>
         </is>
       </c>
       <c r="D166" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_search_click</t>
+          <t>ledger_dashboard_filter_id_input</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>Click</t>
+          <t>Blur</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
@@ -17100,12 +17167,12 @@
       </c>
       <c r="C167" s="9" t="inlineStr">
         <is>
-          <t>重置筛选点击</t>
+          <t>查询点击</t>
         </is>
       </c>
       <c r="D167" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_reset_click</t>
+          <t>ledger_dashboard_search_click</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
@@ -17137,12 +17204,12 @@
       </c>
       <c r="C168" s="9" t="inlineStr">
         <is>
-          <t>流水行查看详情点击</t>
+          <t>重置筛选点击</t>
         </is>
       </c>
       <c r="D168" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_row_detail_click</t>
+          <t>ledger_dashboard_reset_click</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
@@ -17150,9 +17217,9 @@
           <t>Click</t>
         </is>
       </c>
-      <c r="F168" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="F168" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="G168" s="9" t="inlineStr">
@@ -17174,22 +17241,22 @@
       </c>
       <c r="C169" s="9" t="inlineStr">
         <is>
-          <t>流水详情抽屉曝光</t>
+          <t>流水行查看详情点击</t>
         </is>
       </c>
       <c r="D169" s="17" t="inlineStr">
         <is>
-          <t>ledger_dashboard_detail_drawer_view</t>
+          <t>ledger_dashboard_row_detail_click</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>Expo</t>
-        </is>
-      </c>
-      <c r="F169" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F169" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="G169" s="9" t="inlineStr">
@@ -17211,85 +17278,85 @@
       </c>
       <c r="C170" s="9" t="inlineStr">
         <is>
+          <t>流水详情抽屉曝光</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>ledger_dashboard_detail_drawer_view</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>Expo</t>
+        </is>
+      </c>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>本页独有</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>余额流水看板</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>/dashboard</t>
+        </is>
+      </c>
+      <c r="C171" s="9" t="inlineStr">
+        <is>
           <t>流水详情抽屉关闭点击</t>
         </is>
       </c>
-      <c r="D170" s="17" t="inlineStr">
+      <c r="D171" s="17" t="inlineStr">
         <is>
           <t>ledger_dashboard_detail_close_click</t>
         </is>
       </c>
-      <c r="E170" s="8" t="inlineStr">
-        <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="F170" s="20" t="inlineStr">
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F171" s="20" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G170" s="9" t="inlineStr">
+      <c r="G171" s="9" t="inlineStr">
         <is>
           <t>本页独有</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="30" customHeight="1">
-      <c r="A171" s="14" t="inlineStr">
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="14" t="inlineStr">
         <is>
           <t>关联流水明细页</t>
         </is>
       </c>
-      <c r="B171" s="24" t="inlineStr">
+      <c r="B172" s="24" t="inlineStr">
         <is>
           <t>/transaction-ledger</t>
         </is>
       </c>
-      <c r="C171" s="24" t="n"/>
-      <c r="D171" s="15" t="n"/>
-      <c r="E171" s="15" t="n"/>
-      <c r="F171" s="16" t="n"/>
-      <c r="G171" s="25" t="inlineStr">
+      <c r="C172" s="24" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="15" t="n"/>
+      <c r="F172" s="16" t="n"/>
+      <c r="G172" s="25" t="inlineStr">
         <is>
           <t>无侧边栏入口，仅通过充值详情「查看流水」等场景跳转到访，展示围绕单笔充值单的精简流水信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="8" t="inlineStr">
-        <is>
-          <t>关联流水明细页</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="inlineStr">
-        <is>
-          <t>/transaction-ledger</t>
-        </is>
-      </c>
-      <c r="C172" s="9" t="inlineStr">
-        <is>
-          <t>关联流水明细页浏览</t>
-        </is>
-      </c>
-      <c r="D172" s="17" t="inlineStr">
-        <is>
-          <t>transaction_ledger_pv</t>
-        </is>
-      </c>
-      <c r="E172" s="8" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="F172" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="G172" s="9" t="inlineStr">
-        <is>
-          <t>本页独有</t>
         </is>
       </c>
     </row>
@@ -17306,25 +17373,62 @@
       </c>
       <c r="C173" s="9" t="inlineStr">
         <is>
+          <t>关联流水明细页浏览</t>
+        </is>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
+        <is>
+          <t>transaction_ledger_pv</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G173" s="9" t="inlineStr">
+        <is>
+          <t>本页独有</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>关联流水明细页</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>/transaction-ledger</t>
+        </is>
+      </c>
+      <c r="C174" s="9" t="inlineStr">
+        <is>
           <t>流水筛选使用</t>
         </is>
       </c>
-      <c r="D173" s="17" t="inlineStr">
+      <c r="D174" s="17" t="inlineStr">
         <is>
           <t>transaction_ledger_filter_use</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
-        <is>
-          <t>Click</t>
-        </is>
-      </c>
-      <c r="F173" s="20" t="inlineStr">
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>Click</t>
+        </is>
+      </c>
+      <c r="F174" s="20" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G173" s="9" t="inlineStr">
+      <c r="G174" s="9" t="inlineStr">
         <is>
           <t>本页独有</t>
         </is>
@@ -17332,9 +17436,9 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C172:F172"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C79:F79"/>
-    <mergeCell ref="C171:F171"/>
     <mergeCell ref="C130:F130"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C156:F156"/>
